--- a/artfynd/A 45317-2024 artfynd.xlsx
+++ b/artfynd/A 45317-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150338</v>
       </c>
       <c r="B2" t="n">
-        <v>91975</v>
+        <v>91985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150337</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 45317-2024 artfynd.xlsx
+++ b/artfynd/A 45317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150338</v>
+        <v>121150337</v>
       </c>
       <c r="B2" t="n">
-        <v>91985</v>
+        <v>92008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750545</v>
+        <v>750595</v>
       </c>
       <c r="R2" t="n">
-        <v>7296220</v>
+        <v>7296207</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150337</v>
+        <v>121150338</v>
       </c>
       <c r="B3" t="n">
-        <v>92008</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750595</v>
+        <v>750545</v>
       </c>
       <c r="R3" t="n">
-        <v>7296207</v>
+        <v>7296220</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 45317-2024 artfynd.xlsx
+++ b/artfynd/A 45317-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150337</v>
       </c>
       <c r="B2" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150338</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>91997</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 45317-2024 artfynd.xlsx
+++ b/artfynd/A 45317-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150337</v>
       </c>
       <c r="B2" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150338</v>
       </c>
       <c r="B3" t="n">
-        <v>91997</v>
+        <v>91998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 45317-2024 artfynd.xlsx
+++ b/artfynd/A 45317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150337</v>
+        <v>121150338</v>
       </c>
       <c r="B2" t="n">
-        <v>92021</v>
+        <v>92001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750595</v>
+        <v>750545</v>
       </c>
       <c r="R2" t="n">
-        <v>7296207</v>
+        <v>7296220</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150338</v>
+        <v>121150337</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>92024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750545</v>
+        <v>750595</v>
       </c>
       <c r="R3" t="n">
-        <v>7296220</v>
+        <v>7296207</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
